--- a/data/trans_orig/P1_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1_R-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales en 2007</t>
+          <t>Hogares unipersonales en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11456</t>
+          <t>11157</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29559</t>
+          <t>29406</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4621</t>
+          <t>4504</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16951</t>
+          <t>15887</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17663</t>
+          <t>18432</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40084</t>
+          <t>40386</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>464505</t>
+          <t>464658</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>482608</t>
+          <t>482907</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>450538</t>
+          <t>451602</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>462868</t>
+          <t>462985</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>921469</t>
+          <t>921167</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>943890</t>
+          <t>943121</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,08%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36858</t>
+          <t>38905</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67328</t>
+          <t>67015</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15560</t>
+          <t>16257</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36548</t>
+          <t>36774</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>59955</t>
+          <t>59144</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>94080</t>
+          <t>94571</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>668161</t>
+          <t>668474</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>698631</t>
+          <t>696584</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>588946</t>
+          <t>588720</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>609934</t>
+          <t>609237</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1266902</t>
+          <t>1266411</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1301027</t>
+          <t>1301838</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,65%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27792</t>
+          <t>28203</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53916</t>
+          <t>53035</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8404</t>
+          <t>8216</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24196</t>
+          <t>24080</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40991</t>
+          <t>40403</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>69593</t>
+          <t>71493</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>584752</t>
+          <t>585633</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>610876</t>
+          <t>610465</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>665548</t>
+          <t>665664</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>681340</t>
+          <t>681528</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1258819</t>
+          <t>1256919</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1287421</t>
+          <t>1288009</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,96%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21360</t>
+          <t>22065</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44725</t>
+          <t>45221</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15850</t>
+          <t>15971</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36133</t>
+          <t>37070</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41968</t>
+          <t>42747</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>73328</t>
+          <t>73842</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>474422</t>
+          <t>473926</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>497787</t>
+          <t>497082</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>479509</t>
+          <t>478572</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>499792</t>
+          <t>499671</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>961461</t>
+          <t>960947</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>992821</t>
+          <t>992042</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,87%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17574</t>
+          <t>17157</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38531</t>
+          <t>37592</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25828</t>
+          <t>24409</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47881</t>
+          <t>47416</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>47841</t>
+          <t>46625</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>78445</t>
+          <t>76417</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>348179</t>
+          <t>349118</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>369136</t>
+          <t>369553</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>356105</t>
+          <t>356570</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>378158</t>
+          <t>379577</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>712251</t>
+          <t>714279</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>742855</t>
+          <t>744071</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,1%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19238</t>
+          <t>18126</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39398</t>
+          <t>38405</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>60532</t>
+          <t>61462</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>89312</t>
+          <t>89127</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>85993</t>
+          <t>86158</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>121023</t>
+          <t>121315</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,09%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>253185</t>
+          <t>254178</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>273345</t>
+          <t>274457</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>253622</t>
+          <t>253807</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>282402</t>
+          <t>281472</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>514494</t>
+          <t>514202</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>549524</t>
+          <t>549359</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,44%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33157</t>
+          <t>31795</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>55835</t>
+          <t>54567</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>95625</t>
+          <t>97965</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>133898</t>
+          <t>132137</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>135749</t>
+          <t>137229</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>177845</t>
+          <t>180517</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>33,2%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>154048</t>
+          <t>155316</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>176726</t>
+          <t>178088</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>200010</t>
+          <t>201771</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>238283</t>
+          <t>235943</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>365946</t>
+          <t>363274</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>408042</t>
+          <t>406562</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>74,76%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>209536</t>
+          <t>208080</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>267820</t>
+          <t>268121</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>263461</t>
+          <t>264324</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>331569</t>
+          <t>329422</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>489298</t>
+          <t>494099</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>577801</t>
+          <t>579992</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3008723</t>
+          <t>3008422</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3067007</t>
+          <t>3068463</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3047628</t>
+          <t>3049775</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3115736</t>
+          <t>3114873</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6077940</t>
+          <t>6075749</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6166443</t>
+          <t>6161642</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,58%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales en 2012</t>
+          <t>Hogares unipersonales en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13643</t>
+          <t>14131</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9513</t>
+          <t>9718</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27336</t>
+          <t>27404</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15854</t>
+          <t>14568</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36776</t>
+          <t>35563</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>440503</t>
+          <t>440015</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>451278</t>
+          <t>451185</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>402894</t>
+          <t>402826</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>420717</t>
+          <t>420512</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>847600</t>
+          <t>848813</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>868522</t>
+          <t>869808</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53377</t>
+          <t>53261</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>85632</t>
+          <t>85714</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17726</t>
+          <t>18310</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39932</t>
+          <t>40370</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>75481</t>
+          <t>77680</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>115691</t>
+          <t>116274</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>601455</t>
+          <t>601373</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>633710</t>
+          <t>633826</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>570323</t>
+          <t>569885</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>592529</t>
+          <t>591945</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1181651</t>
+          <t>1181068</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1221861</t>
+          <t>1219662</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,01%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22377</t>
+          <t>22205</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43672</t>
+          <t>45063</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5762</t>
+          <t>5676</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20547</t>
+          <t>21384</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30389</t>
+          <t>32345</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58335</t>
+          <t>60112</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>638191</t>
+          <t>636800</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>659486</t>
+          <t>659658</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>690303</t>
+          <t>689466</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>705088</t>
+          <t>705174</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1334377</t>
+          <t>1332600</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1362323</t>
+          <t>1360367</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39013</t>
+          <t>39081</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69969</t>
+          <t>71027</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18851</t>
+          <t>19727</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41786</t>
+          <t>43002</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>66184</t>
+          <t>63416</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>103074</t>
+          <t>101680</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>544648</t>
+          <t>543590</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>575604</t>
+          <t>575536</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>574413</t>
+          <t>573197</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>597348</t>
+          <t>596472</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1127742</t>
+          <t>1129136</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1164632</t>
+          <t>1167400</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,85%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21119</t>
+          <t>20971</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43027</t>
+          <t>43644</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27603</t>
+          <t>26809</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51624</t>
+          <t>51921</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>54127</t>
+          <t>53240</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>87670</t>
+          <t>87300</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,95%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>386402</t>
+          <t>385785</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>408310</t>
+          <t>408458</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>396176</t>
+          <t>395879</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>420197</t>
+          <t>420991</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>789559</t>
+          <t>789929</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>823102</t>
+          <t>823989</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,93%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27309</t>
+          <t>26619</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50886</t>
+          <t>50855</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>69369</t>
+          <t>69123</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>102865</t>
+          <t>100558</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>102079</t>
+          <t>102650</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>141513</t>
+          <t>144316</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,74%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>258900</t>
+          <t>258931</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>282477</t>
+          <t>283167</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>251131</t>
+          <t>253438</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>284627</t>
+          <t>284873</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>522269</t>
+          <t>519466</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>561703</t>
+          <t>561132</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>78,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,54%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43515</t>
+          <t>43003</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>70946</t>
+          <t>71496</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>127884</t>
+          <t>126703</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>166322</t>
+          <t>165492</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>176988</t>
+          <t>179234</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>228062</t>
+          <t>228674</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,8%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>178905</t>
+          <t>178355</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>206336</t>
+          <t>206848</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>222657</t>
+          <t>223487</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>261095</t>
+          <t>262276</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>410768</t>
+          <t>410156</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>461842</t>
+          <t>459596</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>64,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>71,94%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>252379</t>
+          <t>252517</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>322286</t>
+          <t>323157</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>316856</t>
+          <t>319615</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>391205</t>
+          <t>393320</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>591395</t>
+          <t>592116</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>689537</t>
+          <t>694341</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3104493</t>
+          <t>3103622</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3174400</t>
+          <t>3174262</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3167104</t>
+          <t>3164989</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3241453</t>
+          <t>3238694</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6295551</t>
+          <t>6290747</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6393693</t>
+          <t>6392972</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,52%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales en 2016</t>
+          <t>Hogares unipersonales en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19829</t>
+          <t>19342</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42755</t>
+          <t>42547</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20015</t>
+          <t>20091</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40350</t>
+          <t>41358</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45040</t>
+          <t>45264</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>76672</t>
+          <t>76105</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,34%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>376708</t>
+          <t>376916</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399634</t>
+          <t>400121</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>355405</t>
+          <t>354397</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>375740</t>
+          <t>375664</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>738546</t>
+          <t>739113</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>770178</t>
+          <t>769954</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,45%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>48547</t>
+          <t>48651</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>78092</t>
+          <t>78514</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31861</t>
+          <t>29796</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55499</t>
+          <t>53474</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>87420</t>
+          <t>86004</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>125523</t>
+          <t>123865</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,73%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>512404</t>
+          <t>511982</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>541949</t>
+          <t>541845</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>508045</t>
+          <t>510070</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>531683</t>
+          <t>533748</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1028517</t>
+          <t>1030175</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1066620</t>
+          <t>1068036</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,55%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57564</t>
+          <t>57728</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>91656</t>
+          <t>89765</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21144</t>
+          <t>19481</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41589</t>
+          <t>40699</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>84084</t>
+          <t>85453</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>123213</t>
+          <t>124963</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>577441</t>
+          <t>579332</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>611533</t>
+          <t>611369</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>619797</t>
+          <t>620687</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>640242</t>
+          <t>641905</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1207270</t>
+          <t>1205520</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1246399</t>
+          <t>1245030</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,58%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67298</t>
+          <t>66930</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>103168</t>
+          <t>106562</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24366</t>
+          <t>25322</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49470</t>
+          <t>49794</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>96937</t>
+          <t>98157</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>142620</t>
+          <t>142986</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,04%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>542880</t>
+          <t>539486</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>578750</t>
+          <t>579118</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>599607</t>
+          <t>599283</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>624711</t>
+          <t>623755</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1152505</t>
+          <t>1152139</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1198188</t>
+          <t>1196968</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,42%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>42440</t>
+          <t>41279</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>70913</t>
+          <t>71585</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>61533</t>
+          <t>59704</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>95973</t>
+          <t>93862</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>109034</t>
+          <t>108811</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>154529</t>
+          <t>154562</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,86%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>407005</t>
+          <t>406333</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>435478</t>
+          <t>436639</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>400876</t>
+          <t>402987</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>435316</t>
+          <t>437145</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>820238</t>
+          <t>820205</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>865733</t>
+          <t>865956</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>88,84%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41543</t>
+          <t>41826</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>67898</t>
+          <t>67605</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>77535</t>
+          <t>76780</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>112979</t>
+          <t>111836</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>126381</t>
+          <t>127665</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>170486</t>
+          <t>169909</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,86%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>266432</t>
+          <t>266725</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>292787</t>
+          <t>292504</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>264783</t>
+          <t>265926</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>300227</t>
+          <t>300982</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>541606</t>
+          <t>542183</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>585711</t>
+          <t>584427</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,07%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55357</t>
+          <t>55537</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>80775</t>
+          <t>81371</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>140846</t>
+          <t>137628</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>184685</t>
+          <t>183530</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>203471</t>
+          <t>203407</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>256336</t>
+          <t>256751</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>39,07%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>176223</t>
+          <t>175627</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>201641</t>
+          <t>201461</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>215484</t>
+          <t>216639</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>259323</t>
+          <t>262541</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>400831</t>
+          <t>400416</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>453696</t>
+          <t>453760</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>69,05%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>391908</t>
+          <t>385915</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>467061</t>
+          <t>462648</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>422524</t>
+          <t>426087</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>510518</t>
+          <t>512579</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>834114</t>
+          <t>834380</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>953145</t>
+          <t>950192</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,69%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2927289</t>
+          <t>2931702</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3002442</t>
+          <t>3008435</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3034024</t>
+          <t>3031963</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3122018</t>
+          <t>3118455</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5985747</t>
+          <t>5988700</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6104778</t>
+          <t>6104512</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,7 +9290,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales en 2023</t>
+          <t>Hogares unipersonales en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6340</t>
+          <t>6199</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43437</t>
+          <t>41391</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7797</t>
+          <t>7786</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26529</t>
+          <t>26293</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18519</t>
+          <t>18330</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52490</t>
+          <t>56404</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>356550</t>
+          <t>358596</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>393647</t>
+          <t>393788</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>286671</t>
+          <t>286907</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>305403</t>
+          <t>305414</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>660697</t>
+          <t>656783</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>694668</t>
+          <t>694857</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,43%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51940</t>
+          <t>51466</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89935</t>
+          <t>89008</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23548</t>
+          <t>23873</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56798</t>
+          <t>56380</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>80276</t>
+          <t>79722</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>132718</t>
+          <t>134868</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,41%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>333612</t>
+          <t>334539</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>371607</t>
+          <t>372081</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>455295</t>
+          <t>455713</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>488545</t>
+          <t>488220</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>802922</t>
+          <t>800772</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>855364</t>
+          <t>855918</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,48%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>64685</t>
+          <t>66921</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>99379</t>
+          <t>103572</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22718</t>
+          <t>23478</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43790</t>
+          <t>45121</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>93374</t>
+          <t>96064</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>138574</t>
+          <t>139943</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>436959</t>
+          <t>432766</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>471653</t>
+          <t>469417</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>548212</t>
+          <t>546881</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>569284</t>
+          <t>568524</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>989766</t>
+          <t>988397</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1034966</t>
+          <t>1032276</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,49%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57150</t>
+          <t>54010</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>191573</t>
+          <t>191743</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37802</t>
+          <t>38180</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60483</t>
+          <t>59808</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>103956</t>
+          <t>109971</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>224484</t>
+          <t>226860</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,17%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>696213</t>
+          <t>696043</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>830636</t>
+          <t>833776</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>652398</t>
+          <t>653073</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>675079</t>
+          <t>674701</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1376183</t>
+          <t>1373807</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1496711</t>
+          <t>1490696</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,13%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>93542</t>
+          <t>91770</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>130505</t>
+          <t>128186</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,82 +11057,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>16,35%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>22,84%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>93351</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>80108</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>107926</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>17,04%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>14,62%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>19,7%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>204983</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>184857</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>229211</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>18,48%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>16,67%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>23,25%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>93351</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>79338</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>106327</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>17,04%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>14,48%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>19,41%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>204983</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>186323</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>229045</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>18,48%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>16,8%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,67%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>430729</t>
+          <t>433048</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>467692</t>
+          <t>469464</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,82 +11170,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>83,65%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>833</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>454554</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>439979</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>467797</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>82,96%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>80,3%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>85,38%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>1365</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>904156</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>879928</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>924282</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>81,52%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>79,33%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>83,33%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>833</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>454554</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>441578</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>468567</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>82,96%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>80,59%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>85,52%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1365</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>904156</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>880094</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>922816</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>81,52%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>79,35%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>83,2%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>69232</t>
+          <t>68035</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>93994</t>
+          <t>94717</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>55814</t>
+          <t>60579</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>207103</t>
+          <t>207109</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,7 +11435,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>114506</t>
+          <t>116077</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>275953</t>
+          <t>278946</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,56%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>274171</t>
+          <t>273448</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>298933</t>
+          <t>300130</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>401265</t>
+          <t>401259</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>552554</t>
+          <t>547789</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>700580</t>
+          <t>697587</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>862027</t>
+          <t>860456</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,11%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>76879</t>
+          <t>77405</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>102018</t>
+          <t>100815</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>224307</t>
+          <t>223598</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>252627</t>
+          <t>251915</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>306526</t>
+          <t>308654</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>346289</t>
+          <t>346469</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>48,9%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>180741</t>
+          <t>181944</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>205880</t>
+          <t>205354</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>64,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>173204</t>
+          <t>173916</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>201524</t>
+          <t>202233</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>362301</t>
+          <t>362121</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>402064</t>
+          <t>399936</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>56,44%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>446849</t>
+          <t>465285</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>643924</t>
+          <t>645945</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>488579</t>
+          <t>493102</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>659073</t>
+          <t>660438</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1025000</t>
+          <t>1029354</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1279680</t>
+          <t>1279637</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,7 +12156,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2815893</t>
+          <t>2813872</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3012968</t>
+          <t>2994532</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3053207</t>
+          <t>3051842</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3223701</t>
+          <t>3219178</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5892417</t>
+          <t>5892460</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6147097</t>
+          <t>6142743</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,65%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1_R-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>10712</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29406</t>
+          <t>29329</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4504</t>
+          <t>3805</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15887</t>
+          <t>15620</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18432</t>
+          <t>16797</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40386</t>
+          <t>39240</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>464658</t>
+          <t>464735</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>482907</t>
+          <t>483352</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>451602</t>
+          <t>451869</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>462985</t>
+          <t>463684</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>921167</t>
+          <t>922313</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>943121</t>
+          <t>944756</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38905</t>
+          <t>38450</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67015</t>
+          <t>68249</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16257</t>
+          <t>14885</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36774</t>
+          <t>34971</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>59144</t>
+          <t>59207</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>94571</t>
+          <t>93120</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>668474</t>
+          <t>667240</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>696584</t>
+          <t>697039</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>588720</t>
+          <t>590523</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>609237</t>
+          <t>610609</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1266411</t>
+          <t>1267862</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1301838</t>
+          <t>1301775</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53035</t>
+          <t>54010</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8216</t>
+          <t>7861</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24080</t>
+          <t>23252</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40403</t>
+          <t>40705</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71493</t>
+          <t>72426</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>585633</t>
+          <t>584658</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>665664</t>
+          <t>666492</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>681528</t>
+          <t>681883</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1256919</t>
+          <t>1255986</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1288009</t>
+          <t>1287707</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,94%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22065</t>
+          <t>21403</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45221</t>
+          <t>44911</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15971</t>
+          <t>15620</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37070</t>
+          <t>36285</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42747</t>
+          <t>41005</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>73842</t>
+          <t>72294</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>473926</t>
+          <t>474236</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>497082</t>
+          <t>497744</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>478572</t>
+          <t>479357</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>499671</t>
+          <t>500022</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>960947</t>
+          <t>962495</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>992042</t>
+          <t>993784</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>96,04%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17157</t>
+          <t>16507</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37592</t>
+          <t>37754</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24409</t>
+          <t>24374</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47416</t>
+          <t>46912</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>46625</t>
+          <t>48565</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>76417</t>
+          <t>81319</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>349118</t>
+          <t>348956</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>369553</t>
+          <t>370203</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>356570</t>
+          <t>357074</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>379577</t>
+          <t>379612</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>714279</t>
+          <t>709377</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>744071</t>
+          <t>742131</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,86%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18126</t>
+          <t>18161</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>38405</t>
+          <t>39185</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>61462</t>
+          <t>60369</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>89127</t>
+          <t>89600</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>86158</t>
+          <t>84313</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>121315</t>
+          <t>120001</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,88%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>254178</t>
+          <t>253398</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>274457</t>
+          <t>274422</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>253807</t>
+          <t>253334</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>281472</t>
+          <t>282565</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>514202</t>
+          <t>515516</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>549359</t>
+          <t>551204</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,73%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31795</t>
+          <t>32458</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>54567</t>
+          <t>55267</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>97965</t>
+          <t>97472</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>132137</t>
+          <t>135280</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>137229</t>
+          <t>136615</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>180517</t>
+          <t>179380</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>32,99%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>155316</t>
+          <t>154616</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>178088</t>
+          <t>177425</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>201771</t>
+          <t>198628</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>235943</t>
+          <t>236436</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>363274</t>
+          <t>364411</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>406562</t>
+          <t>407176</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>74,88%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>208080</t>
+          <t>209412</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>268121</t>
+          <t>271884</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>264324</t>
+          <t>261588</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>329422</t>
+          <t>329584</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>494099</t>
+          <t>489979</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>579992</t>
+          <t>582606</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3008422</t>
+          <t>3004659</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3068463</t>
+          <t>3067131</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3049775</t>
+          <t>3049613</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3114873</t>
+          <t>3117609</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6075749</t>
+          <t>6073135</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6161642</t>
+          <t>6165762</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,64%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>2676</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14131</t>
+          <t>13962</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9718</t>
+          <t>9664</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27404</t>
+          <t>27045</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14568</t>
+          <t>15279</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35563</t>
+          <t>36773</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>440015</t>
+          <t>440184</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>451185</t>
+          <t>451470</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>402826</t>
+          <t>403185</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>420512</t>
+          <t>420566</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>848813</t>
+          <t>847603</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>869808</t>
+          <t>869097</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53261</t>
+          <t>54844</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>85714</t>
+          <t>88896</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18310</t>
+          <t>18728</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40370</t>
+          <t>40120</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>77680</t>
+          <t>76811</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>116274</t>
+          <t>117221</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>601373</t>
+          <t>598191</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>633826</t>
+          <t>632243</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>569885</t>
+          <t>570135</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>591945</t>
+          <t>591527</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1181068</t>
+          <t>1180121</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1219662</t>
+          <t>1220531</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,08%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22205</t>
+          <t>21502</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45063</t>
+          <t>43137</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5676</t>
+          <t>5602</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21384</t>
+          <t>21224</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32345</t>
+          <t>31734</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60112</t>
+          <t>57634</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>636800</t>
+          <t>638726</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>659658</t>
+          <t>660361</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>689466</t>
+          <t>689626</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>705174</t>
+          <t>705248</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1332600</t>
+          <t>1335078</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1360367</t>
+          <t>1360978</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,72%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39081</t>
+          <t>39689</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71027</t>
+          <t>71221</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19727</t>
+          <t>19456</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43002</t>
+          <t>41916</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>63416</t>
+          <t>63271</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>101680</t>
+          <t>102606</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>543590</t>
+          <t>543396</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>575536</t>
+          <t>574928</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>573197</t>
+          <t>574283</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>596472</t>
+          <t>596743</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1129136</t>
+          <t>1128210</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1167400</t>
+          <t>1167545</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,86%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20971</t>
+          <t>20570</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43644</t>
+          <t>42883</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26809</t>
+          <t>26839</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51921</t>
+          <t>52575</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>53240</t>
+          <t>54500</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>87300</t>
+          <t>89649</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>385785</t>
+          <t>386546</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>408458</t>
+          <t>408859</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>395879</t>
+          <t>395225</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>420991</t>
+          <t>420961</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>789929</t>
+          <t>787580</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>823989</t>
+          <t>822729</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,79%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26619</t>
+          <t>24997</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50855</t>
+          <t>51817</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>69123</t>
+          <t>67135</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>100558</t>
+          <t>101891</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>102650</t>
+          <t>103946</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>144316</t>
+          <t>147506</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>22,22%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>258931</t>
+          <t>257969</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>283167</t>
+          <t>284789</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>253438</t>
+          <t>252105</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>284873</t>
+          <t>286861</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>519466</t>
+          <t>516276</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>561132</t>
+          <t>559836</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,34%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43003</t>
+          <t>44058</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>71496</t>
+          <t>70664</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>126703</t>
+          <t>124811</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>165492</t>
+          <t>165759</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>179234</t>
+          <t>175870</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>228674</t>
+          <t>227433</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,6%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>178355</t>
+          <t>179187</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>206848</t>
+          <t>205793</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>223487</t>
+          <t>223220</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>262276</t>
+          <t>264168</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>410156</t>
+          <t>411397</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>459596</t>
+          <t>462960</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>64,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>72,47%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>252517</t>
+          <t>255201</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>323157</t>
+          <t>322954</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>319615</t>
+          <t>318571</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>393320</t>
+          <t>393250</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>592116</t>
+          <t>595702</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>694341</t>
+          <t>691765</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,9%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3103622</t>
+          <t>3103825</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3174262</t>
+          <t>3171578</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3164989</t>
+          <t>3165059</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3238694</t>
+          <t>3239738</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6290747</t>
+          <t>6293323</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6392972</t>
+          <t>6389386</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,47%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19342</t>
+          <t>20652</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42547</t>
+          <t>43978</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20091</t>
+          <t>19910</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41358</t>
+          <t>40788</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45264</t>
+          <t>43822</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>76105</t>
+          <t>74747</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>376916</t>
+          <t>375485</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>400121</t>
+          <t>398811</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>354397</t>
+          <t>354967</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>375664</t>
+          <t>375845</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>739113</t>
+          <t>740471</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>769954</t>
+          <t>771396</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,62%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>48651</t>
+          <t>48540</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>78514</t>
+          <t>79046</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29796</t>
+          <t>31687</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53474</t>
+          <t>54515</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>86004</t>
+          <t>86980</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>123865</t>
+          <t>123520</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,7%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>511982</t>
+          <t>511450</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>541845</t>
+          <t>541956</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>510070</t>
+          <t>509029</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>533748</t>
+          <t>531857</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1030175</t>
+          <t>1030520</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1068036</t>
+          <t>1067060</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,46%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57728</t>
+          <t>58064</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>89765</t>
+          <t>91404</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19481</t>
+          <t>20103</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40699</t>
+          <t>40816</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>85453</t>
+          <t>83871</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>124963</t>
+          <t>122893</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>579332</t>
+          <t>577693</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>611369</t>
+          <t>611033</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>620687</t>
+          <t>620570</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>641905</t>
+          <t>641283</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1205520</t>
+          <t>1207590</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1245030</t>
+          <t>1246612</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,7%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66930</t>
+          <t>66518</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>106562</t>
+          <t>102108</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25322</t>
+          <t>24107</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49794</t>
+          <t>49502</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>98157</t>
+          <t>98803</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>142986</t>
+          <t>141167</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,9%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>539486</t>
+          <t>543940</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>579118</t>
+          <t>579530</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>599283</t>
+          <t>599575</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>623755</t>
+          <t>624970</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1152139</t>
+          <t>1153958</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1196968</t>
+          <t>1196322</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,37%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>41279</t>
+          <t>42581</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>71585</t>
+          <t>71800</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>59704</t>
+          <t>60864</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>93862</t>
+          <t>94260</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>108811</t>
+          <t>108812</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>154562</t>
+          <t>155848</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,99%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>406333</t>
+          <t>406118</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>436639</t>
+          <t>435337</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>402987</t>
+          <t>402589</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>437145</t>
+          <t>435985</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>820205</t>
+          <t>818919</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>865956</t>
+          <t>865955</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41826</t>
+          <t>41157</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>67605</t>
+          <t>68944</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>76780</t>
+          <t>78225</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>111836</t>
+          <t>111879</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>127665</t>
+          <t>124875</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>169909</t>
+          <t>169171</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,76%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>266725</t>
+          <t>265386</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>292504</t>
+          <t>293173</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>265926</t>
+          <t>265883</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>300982</t>
+          <t>299537</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>542183</t>
+          <t>542921</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>584427</t>
+          <t>587217</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>82,46%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55537</t>
+          <t>54511</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>81371</t>
+          <t>80816</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>137628</t>
+          <t>141683</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>183530</t>
+          <t>185513</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>203407</t>
+          <t>203262</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>256751</t>
+          <t>255983</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>38,95%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>175627</t>
+          <t>176182</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>201461</t>
+          <t>202487</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>216639</t>
+          <t>214656</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>262541</t>
+          <t>258486</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>400416</t>
+          <t>401184</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>453760</t>
+          <t>453905</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>69,07%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>385915</t>
+          <t>385870</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>462648</t>
+          <t>468053</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>426087</t>
+          <t>426715</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>512579</t>
+          <t>512088</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>834380</t>
+          <t>832352</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>950192</t>
+          <t>950207</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2931702</t>
+          <t>2926297</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3008435</t>
+          <t>3008480</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3031963</t>
+          <t>3032454</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3118455</t>
+          <t>3117827</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5988700</t>
+          <t>5988685</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6104512</t>
+          <t>6106540</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,0%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>16257</t>
+          <t>26890</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6199</t>
+          <t>13130</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41391</t>
+          <t>49858</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>15085</t>
+          <t>17079</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7786</t>
+          <t>8920</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26293</t>
+          <t>30729</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>31342</t>
+          <t>43969</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18330</t>
+          <t>26773</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56404</t>
+          <t>66730</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>383730</t>
+          <t>380903</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>358596</t>
+          <t>357935</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>393788</t>
+          <t>394663</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>298115</t>
+          <t>345433</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>286907</t>
+          <t>331783</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>305414</t>
+          <t>353592</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>681845</t>
+          <t>726336</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>656783</t>
+          <t>703575</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>694857</t>
+          <t>743532</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>96,52%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>67680</t>
+          <t>75783</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51466</t>
+          <t>57593</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89008</t>
+          <t>98192</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>39990</t>
+          <t>44031</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23873</t>
+          <t>32800</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56380</t>
+          <t>59704</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>107670</t>
+          <t>119815</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>79722</t>
+          <t>96509</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>134868</t>
+          <t>144035</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,72%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>355867</t>
+          <t>401107</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>334539</t>
+          <t>378698</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>372081</t>
+          <t>419297</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>472103</t>
+          <t>457702</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>455713</t>
+          <t>442029</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>488220</t>
+          <t>468933</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>827970</t>
+          <t>858808</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>800772</t>
+          <t>834588</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>855918</t>
+          <t>882114</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>90,14%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>83029</t>
+          <t>98670</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>66921</t>
+          <t>79276</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>103572</t>
+          <t>120030</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>33343</t>
+          <t>35942</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23478</t>
+          <t>26407</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45121</t>
+          <t>47144</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>116372</t>
+          <t>134612</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>96064</t>
+          <t>113727</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>139943</t>
+          <t>159500</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,82%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>453309</t>
+          <t>522167</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>432766</t>
+          <t>500807</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>469417</t>
+          <t>541561</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>558659</t>
+          <t>587251</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>546881</t>
+          <t>576049</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>568524</t>
+          <t>596786</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1011968</t>
+          <t>1109417</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>988397</t>
+          <t>1084529</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1032276</t>
+          <t>1130302</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>90,86%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>132097</t>
+          <t>144754</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>54010</t>
+          <t>121455</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>191743</t>
+          <t>169145</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>49120</t>
+          <t>54609</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38180</t>
+          <t>44459</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59808</t>
+          <t>66160</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>181217</t>
+          <t>199363</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>109971</t>
+          <t>174507</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>226860</t>
+          <t>226747</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>15,77%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>755689</t>
+          <t>555863</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>696043</t>
+          <t>531472</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>833776</t>
+          <t>579162</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>663761</t>
+          <t>682277</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>653073</t>
+          <t>670726</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>674701</t>
+          <t>692427</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1419450</t>
+          <t>1238141</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1373807</t>
+          <t>1210757</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1490696</t>
+          <t>1262997</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>87,86%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>111632</t>
+          <t>121036</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>91770</t>
+          <t>102632</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>128186</t>
+          <t>141818</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>93351</t>
+          <t>101959</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>80108</t>
+          <t>87379</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>107926</t>
+          <t>116148</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>204983</t>
+          <t>222995</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>184857</t>
+          <t>199402</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>229211</t>
+          <t>245338</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,14%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>449602</t>
+          <t>488310</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>433048</t>
+          <t>467528</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>469464</t>
+          <t>506714</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>454554</t>
+          <t>506896</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>439979</t>
+          <t>492707</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>467797</t>
+          <t>521476</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>904156</t>
+          <t>995207</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>879928</t>
+          <t>972864</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>924282</t>
+          <t>1018800</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,63%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>80300</t>
+          <t>88099</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>68035</t>
+          <t>74203</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>94717</t>
+          <t>101651</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>132880</t>
+          <t>143912</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>60579</t>
+          <t>129345</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>207109</t>
+          <t>158308</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>213180</t>
+          <t>232011</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>116077</t>
+          <t>212279</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>278946</t>
+          <t>254599</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>30,09%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>287865</t>
+          <t>318981</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>273448</t>
+          <t>305429</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>300130</t>
+          <t>332877</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>475488</t>
+          <t>295254</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>401259</t>
+          <t>280858</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>547789</t>
+          <t>309821</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>763353</t>
+          <t>614235</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>697587</t>
+          <t>591647</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>860456</t>
+          <t>633967</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>74,92%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,27 +11723,27 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>88396</t>
+          <t>95744</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>77405</t>
+          <t>83382</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>100815</t>
+          <t>110575</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>238741</t>
+          <t>260002</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>223598</t>
+          <t>243723</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>251915</t>
+          <t>274088</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>327138</t>
+          <t>355746</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>308654</t>
+          <t>333220</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>346469</t>
+          <t>375094</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>48,41%</t>
         </is>
       </c>
     </row>
@@ -11836,22 +11836,22 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>194363</t>
+          <t>214454</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>181944</t>
+          <t>199623</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>205354</t>
+          <t>226816</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -11861,7 +11861,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>187090</t>
+          <t>204607</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>173916</t>
+          <t>190521</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>202233</t>
+          <t>220886</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>381452</t>
+          <t>419061</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>362121</t>
+          <t>399713</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>399936</t>
+          <t>441587</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>56,99%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>579391</t>
+          <t>650977</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>465285</t>
+          <t>601919</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>645945</t>
+          <t>699677</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>602510</t>
+          <t>657534</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>493102</t>
+          <t>618777</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>660438</t>
+          <t>694281</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1181902</t>
+          <t>1308510</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1029354</t>
+          <t>1249391</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1279637</t>
+          <t>1369989</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,85%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2880426</t>
+          <t>2881785</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2813872</t>
+          <t>2833085</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2994532</t>
+          <t>2930843</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3109770</t>
+          <t>3079420</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3051842</t>
+          <t>3042673</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3219178</t>
+          <t>3118177</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>5990195</t>
+          <t>5961206</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5892460</t>
+          <t>5899727</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6142743</t>
+          <t>6020325</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>82,81%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">

--- a/data/trans_orig/P1_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1_R-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si conforma un hogar unipersonal en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si conforma un hogar unipersonal en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si conforma un hogar unipersonal en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si conforma un hogar unipersonal en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
